--- a/Treinamento/Cópia de GeraBlocoBCadastroCorretor (1).xlsx
+++ b/Treinamento/Cópia de GeraBlocoBCadastroCorretor (1).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\WWG00M.ROOTDOM.NET\BFS-HOME\BE00572-R0407280\ICM\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C04A9E64-A294-4C6A-B742-067452B5701B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A9D28A0-762C-4CA1-8939-6FCC2708897D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="390" windowWidth="25440" windowHeight="15390" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4110" yWindow="2100" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GeraBlocoBCadastroCorretor" sheetId="2" r:id="rId1"/>
@@ -149,7 +149,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -162,6 +162,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Moeda 2" xfId="2" xr:uid="{9C500936-D842-4095-84AB-BAB79AFDFC42}"/>
@@ -505,194 +508,152 @@
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="7">
-        <v>4034935</v>
+      <c r="A2" s="8">
+        <v>4035139</v>
       </c>
       <c r="B2" s="4"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="7">
-        <v>4034934</v>
+      <c r="A3" s="8">
+        <v>4035138</v>
       </c>
       <c r="B3" s="4"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="7">
-        <v>4034936</v>
+      <c r="A4" s="8">
+        <v>4035128</v>
       </c>
       <c r="B4" s="4"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="7">
-        <v>4034998</v>
+      <c r="A5" s="8">
+        <v>4035121</v>
       </c>
       <c r="B5" s="4"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="7">
-        <v>4034929</v>
+      <c r="A6" s="8">
+        <v>4035123</v>
       </c>
       <c r="B6" s="4"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="7">
-        <v>4034941</v>
+      <c r="A7" s="8">
+        <v>4035122</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="7">
-        <v>4034944</v>
+      <c r="A8" s="8">
+        <v>4035129</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="7">
-        <v>4034973</v>
+      <c r="A9" s="8">
+        <v>4035130</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="7">
-        <v>4035041</v>
+      <c r="A10" s="8">
+        <v>4035134</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="7">
-        <v>4035026</v>
+      <c r="A11" s="8">
+        <v>4035135</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="7">
-        <v>4035030</v>
+      <c r="A12" s="8">
+        <v>4035136</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="7">
-        <v>4035031</v>
+      <c r="A13" s="8">
+        <v>4035137</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="7">
-        <v>4035033</v>
+      <c r="A14" s="8">
+        <v>4035142</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="7">
-        <v>4035131</v>
+      <c r="A15" s="8">
+        <v>4035143</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="7">
-        <v>4035144</v>
+      <c r="A16" s="8">
+        <v>4034938</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="7">
-        <v>4035034</v>
+      <c r="A17" s="8">
+        <v>4034978</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="7">
-        <v>4035132</v>
-      </c>
+      <c r="A18" s="8"/>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="7">
-        <v>4035133</v>
-      </c>
+      <c r="A19" s="7"/>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="7">
-        <v>4035141</v>
-      </c>
+      <c r="A20" s="7"/>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="7">
-        <v>4035140</v>
-      </c>
+      <c r="A21" s="7"/>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" s="7">
-        <v>4035139</v>
-      </c>
+      <c r="A22" s="7"/>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="7">
-        <v>4035138</v>
-      </c>
+      <c r="A23" s="7"/>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="7">
-        <v>4035128</v>
-      </c>
+      <c r="A24" s="7"/>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" s="7">
-        <v>4035121</v>
-      </c>
+      <c r="A25" s="7"/>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A26" s="7">
-        <v>4035123</v>
-      </c>
+      <c r="A26" s="7"/>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A27" s="7">
-        <v>4035122</v>
-      </c>
+      <c r="A27" s="7"/>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A28" s="7">
-        <v>4035129</v>
-      </c>
+      <c r="A28" s="7"/>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A29" s="7">
-        <v>4035130</v>
-      </c>
+      <c r="A29" s="7"/>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A30" s="7">
-        <v>4035134</v>
-      </c>
+      <c r="A30" s="7"/>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A31" s="7">
-        <v>4035135</v>
-      </c>
+      <c r="A31" s="7"/>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A32" s="7">
-        <v>4035136</v>
-      </c>
+      <c r="A32" s="7"/>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A33" s="7">
-        <v>4035137</v>
-      </c>
+      <c r="A33" s="7"/>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A34" s="7">
-        <v>4035142</v>
-      </c>
+      <c r="A34" s="7"/>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A35" s="7">
-        <v>4035143</v>
-      </c>
+      <c r="A35" s="7"/>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A36" s="7">
-        <v>4034938</v>
-      </c>
+      <c r="A36" s="7"/>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A37" s="7">
-        <v>4034978</v>
-      </c>
+      <c r="A37" s="7"/>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A38" s="7">
-        <v>4035009</v>
-      </c>
+      <c r="A38" s="7"/>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" s="7"/>
